--- a/data/Ordenes de trabajo.xlsx
+++ b/data/Ordenes de trabajo.xlsx
@@ -5,22 +5,35 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rolan\AndroidStudioProjects\Serviaux\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\autom\StudioProjects\servielecarandroid\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D23738AE-3F62-4CE2-996F-15C115B2AD1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD03E1BD-0C84-470F-AF9D-E8531BBA1958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ordenes de trabajo" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="115">
   <si>
     <t>id_gato</t>
   </si>
@@ -166,9 +179,6 @@
   </si>
   <si>
     <t>2019</t>
-  </si>
-  <si>
-    <t>Pendiente</t>
   </si>
   <si>
     <t>#763</t>
@@ -450,7 +460,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -767,7 +777,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P17"/>
-  <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="21.7109375" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -971,36 +981,36 @@
         <v>740</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B6" s="3">
         <v>46036</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="L6" s="4">
         <v>36</v>
@@ -1014,31 +1024,31 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B7" s="3">
         <v>46036</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>28</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H7" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="J7" s="4">
         <v>419343</v>
@@ -1055,7 +1065,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B8" s="3">
         <v>46032</v>
@@ -1067,7 +1077,7 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>20</v>
@@ -1096,28 +1106,28 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B9" s="3">
         <v>46032</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>47</v>
@@ -1137,28 +1147,28 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B10" s="3">
         <v>46032</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>75</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>39</v>
@@ -1178,28 +1188,28 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B11" s="3">
         <v>46032</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>28</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>32</v>
@@ -1219,31 +1229,31 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B12" s="3">
         <v>46032</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="G12" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="I12" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="J12" s="4">
         <v>89249</v>
@@ -1260,31 +1270,31 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B13" s="3">
         <v>46032</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="G13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H13" s="2" t="s">
+      <c r="I13" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="J13" s="4">
         <v>56804</v>
@@ -1301,28 +1311,28 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B14" s="3">
         <v>46029</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>47</v>
@@ -1342,31 +1352,31 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B15" s="3">
         <v>46028</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="G15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H15" s="2" t="s">
+      <c r="I15" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="J15" s="4">
         <v>353899</v>
@@ -1383,31 +1393,31 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B16" s="3">
         <v>46028</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>28</v>
       </c>
       <c r="F16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="H16" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="I16" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="J16" s="4">
         <v>97269</v>
@@ -1424,31 +1434,31 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B17" s="3">
         <v>46028</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>30</v>
       </c>
       <c r="H17" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>115</v>
       </c>
       <c r="J17" s="4">
         <v>255266</v>
